--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.55676014923231</v>
+        <v>3.177973524250251</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6109532416782</v>
+        <v>3.186779901772707</v>
       </c>
       <c r="E2" t="n">
-        <v>22.19426537662345</v>
+        <v>3.606568123701311</v>
       </c>
       <c r="F2" t="n">
-        <v>22.26002048203665</v>
+        <v>3.617253328330956</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.38032970036959</v>
+        <v>9.811803576310059</v>
       </c>
       <c r="D3" t="n">
-        <v>61.1106982628572</v>
+        <v>9.930488467714294</v>
       </c>
       <c r="E3" t="n">
-        <v>22.19426537662345</v>
+        <v>3.606568123701311</v>
       </c>
       <c r="F3" t="n">
-        <v>22.26002048203665</v>
+        <v>3.617253328330956</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.06052937519479</v>
+        <v>11.54733602346915</v>
       </c>
       <c r="D4" t="n">
-        <v>70.98951615450261</v>
+        <v>11.53579637510667</v>
       </c>
       <c r="E4" t="n">
-        <v>22.19426537662345</v>
+        <v>3.606568123701311</v>
       </c>
       <c r="F4" t="n">
-        <v>22.26002048203665</v>
+        <v>3.617253328330956</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
